--- a/artfynd/A 23118-2026 artfynd.xlsx
+++ b/artfynd/A 23118-2026 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>133883845</v>
       </c>
       <c r="B10" t="n">
-        <v>91918</v>
+        <v>91922</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133883858</v>
+        <v>133883850</v>
       </c>
       <c r="B12" t="n">
         <v>79334</v>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436616</v>
+        <v>436146</v>
       </c>
       <c r="R12" t="n">
-        <v>7034138</v>
+        <v>7034395</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,6 +1766,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1792,32 +1797,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133883837</v>
+        <v>133883858</v>
       </c>
       <c r="B13" t="n">
-        <v>104646</v>
+        <v>79334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1827,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436901</v>
+        <v>436616</v>
       </c>
       <c r="R13" t="n">
-        <v>7034035</v>
+        <v>7034138</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,32 +1894,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133883850</v>
+        <v>133883837</v>
       </c>
       <c r="B14" t="n">
-        <v>79334</v>
+        <v>104650</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>222412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1924,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436146</v>
+        <v>436901</v>
       </c>
       <c r="R14" t="n">
-        <v>7034395</v>
+        <v>7034035</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1960,11 +1965,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 23118-2026 artfynd.xlsx
+++ b/artfynd/A 23118-2026 artfynd.xlsx
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133883833</v>
+        <v>133883852</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436921</v>
+        <v>436245</v>
       </c>
       <c r="R5" t="n">
-        <v>7033984</v>
+        <v>7034366</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133883852</v>
+        <v>133883833</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436245</v>
+        <v>436921</v>
       </c>
       <c r="R6" t="n">
-        <v>7034366</v>
+        <v>7033984</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1504,7 +1504,7 @@
         <v>133883845</v>
       </c>
       <c r="B10" t="n">
-        <v>91922</v>
+        <v>91924</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>133883837</v>
       </c>
       <c r="B14" t="n">
-        <v>104650</v>
+        <v>104652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23118-2026 artfynd.xlsx
+++ b/artfynd/A 23118-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133883835</v>
       </c>
       <c r="B2" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>133883834</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>133883847</v>
       </c>
       <c r="B4" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133883852</v>
+        <v>133883833</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>57965</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436245</v>
+        <v>436921</v>
       </c>
       <c r="R5" t="n">
-        <v>7034366</v>
+        <v>7033984</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133883833</v>
+        <v>133883852</v>
       </c>
       <c r="B6" t="n">
-        <v>57958</v>
+        <v>79348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436921</v>
+        <v>436245</v>
       </c>
       <c r="R6" t="n">
-        <v>7033984</v>
+        <v>7034366</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1208,7 @@
         <v>133883832</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133883855</v>
+        <v>133883845</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>91943</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436337</v>
+        <v>436888</v>
       </c>
       <c r="R8" t="n">
-        <v>7034305</v>
+        <v>7034026</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133883856</v>
+        <v>133883855</v>
       </c>
       <c r="B9" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436376</v>
+        <v>436337</v>
       </c>
       <c r="R9" t="n">
-        <v>7034270</v>
+        <v>7034305</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133883845</v>
+        <v>133883856</v>
       </c>
       <c r="B10" t="n">
-        <v>91924</v>
+        <v>79348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436888</v>
+        <v>436376</v>
       </c>
       <c r="R10" t="n">
-        <v>7034026</v>
+        <v>7034270</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
         <v>133883849</v>
       </c>
       <c r="B11" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>133883850</v>
       </c>
       <c r="B12" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>133883858</v>
       </c>
       <c r="B13" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>133883837</v>
       </c>
       <c r="B14" t="n">
-        <v>104652</v>
+        <v>104680</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>133883853</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 23118-2026 artfynd.xlsx
+++ b/artfynd/A 23118-2026 artfynd.xlsx
@@ -1695,32 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133883850</v>
+        <v>133883837</v>
       </c>
       <c r="B12" t="n">
-        <v>79348</v>
+        <v>104680</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>222412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436146</v>
+        <v>436901</v>
       </c>
       <c r="R12" t="n">
-        <v>7034395</v>
+        <v>7034035</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,11 +1766,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,7 +1792,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133883858</v>
+        <v>133883850</v>
       </c>
       <c r="B13" t="n">
         <v>79348</v>
@@ -1832,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436616</v>
+        <v>436146</v>
       </c>
       <c r="R13" t="n">
-        <v>7034138</v>
+        <v>7034395</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1868,6 +1863,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1894,32 +1894,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133883837</v>
+        <v>133883858</v>
       </c>
       <c r="B14" t="n">
-        <v>104680</v>
+        <v>79348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436901</v>
+        <v>436616</v>
       </c>
       <c r="R14" t="n">
-        <v>7034035</v>
+        <v>7034138</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 23118-2026 artfynd.xlsx
+++ b/artfynd/A 23118-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133883835</v>
       </c>
       <c r="B2" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>133883834</v>
       </c>
       <c r="B3" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>133883847</v>
       </c>
       <c r="B4" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>133883833</v>
       </c>
       <c r="B5" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>133883852</v>
       </c>
       <c r="B6" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>133883832</v>
       </c>
       <c r="B7" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>133883845</v>
       </c>
       <c r="B8" t="n">
-        <v>91943</v>
+        <v>91953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>133883855</v>
       </c>
       <c r="B9" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>133883856</v>
       </c>
       <c r="B10" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>133883849</v>
       </c>
       <c r="B11" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>133883837</v>
       </c>
       <c r="B12" t="n">
-        <v>104680</v>
+        <v>104690</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>133883850</v>
       </c>
       <c r="B13" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>133883858</v>
       </c>
       <c r="B14" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>133883853</v>
       </c>
       <c r="B15" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 23118-2026 artfynd.xlsx
+++ b/artfynd/A 23118-2026 artfynd.xlsx
@@ -1695,32 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133883837</v>
+        <v>133883850</v>
       </c>
       <c r="B12" t="n">
-        <v>104690</v>
+        <v>79358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436901</v>
+        <v>436146</v>
       </c>
       <c r="R12" t="n">
-        <v>7034035</v>
+        <v>7034395</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,6 +1766,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1792,32 +1797,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133883850</v>
+        <v>133883837</v>
       </c>
       <c r="B13" t="n">
-        <v>79358</v>
+        <v>104690</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>222412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1827,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436146</v>
+        <v>436901</v>
       </c>
       <c r="R13" t="n">
-        <v>7034395</v>
+        <v>7034035</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,11 +1868,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 23118-2026 artfynd.xlsx
+++ b/artfynd/A 23118-2026 artfynd.xlsx
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133883845</v>
+        <v>133883856</v>
       </c>
       <c r="B8" t="n">
-        <v>91953</v>
+        <v>79358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436888</v>
+        <v>436376</v>
       </c>
       <c r="R8" t="n">
-        <v>7034026</v>
+        <v>7034270</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133883855</v>
+        <v>133883845</v>
       </c>
       <c r="B9" t="n">
-        <v>79358</v>
+        <v>91953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436337</v>
+        <v>436888</v>
       </c>
       <c r="R9" t="n">
-        <v>7034305</v>
+        <v>7034026</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133883856</v>
+        <v>133883855</v>
       </c>
       <c r="B10" t="n">
         <v>79358</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436376</v>
+        <v>436337</v>
       </c>
       <c r="R10" t="n">
-        <v>7034270</v>
+        <v>7034305</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 23118-2026 artfynd.xlsx
+++ b/artfynd/A 23118-2026 artfynd.xlsx
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133883856</v>
+        <v>133883845</v>
       </c>
       <c r="B8" t="n">
-        <v>79358</v>
+        <v>91953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436376</v>
+        <v>436888</v>
       </c>
       <c r="R8" t="n">
-        <v>7034270</v>
+        <v>7034026</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133883845</v>
+        <v>133883855</v>
       </c>
       <c r="B9" t="n">
-        <v>91953</v>
+        <v>79358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436888</v>
+        <v>436337</v>
       </c>
       <c r="R9" t="n">
-        <v>7034026</v>
+        <v>7034305</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133883855</v>
+        <v>133883856</v>
       </c>
       <c r="B10" t="n">
         <v>79358</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436337</v>
+        <v>436376</v>
       </c>
       <c r="R10" t="n">
-        <v>7034305</v>
+        <v>7034270</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 23118-2026 artfynd.xlsx
+++ b/artfynd/A 23118-2026 artfynd.xlsx
@@ -1695,32 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133883850</v>
+        <v>133883837</v>
       </c>
       <c r="B12" t="n">
-        <v>79358</v>
+        <v>104690</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>222412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436146</v>
+        <v>436901</v>
       </c>
       <c r="R12" t="n">
-        <v>7034395</v>
+        <v>7034035</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,11 +1766,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,32 +1792,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133883837</v>
+        <v>133883858</v>
       </c>
       <c r="B13" t="n">
-        <v>104690</v>
+        <v>79358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1832,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436901</v>
+        <v>436616</v>
       </c>
       <c r="R13" t="n">
-        <v>7034035</v>
+        <v>7034138</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1894,7 +1889,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133883858</v>
+        <v>133883850</v>
       </c>
       <c r="B14" t="n">
         <v>79358</v>
@@ -1929,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436616</v>
+        <v>436146</v>
       </c>
       <c r="R14" t="n">
-        <v>7034138</v>
+        <v>7034395</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1965,6 +1960,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 23118-2026 artfynd.xlsx
+++ b/artfynd/A 23118-2026 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>133883847</v>
       </c>
       <c r="B4" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>133883852</v>
       </c>
       <c r="B6" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>133883845</v>
       </c>
       <c r="B8" t="n">
-        <v>91953</v>
+        <v>91955</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>133883855</v>
       </c>
       <c r="B9" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>133883856</v>
       </c>
       <c r="B10" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>133883849</v>
       </c>
       <c r="B11" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>133883837</v>
       </c>
       <c r="B12" t="n">
-        <v>104690</v>
+        <v>104692</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133883858</v>
+        <v>133883850</v>
       </c>
       <c r="B13" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436616</v>
+        <v>436146</v>
       </c>
       <c r="R13" t="n">
-        <v>7034138</v>
+        <v>7034395</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,6 +1863,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1889,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133883850</v>
+        <v>133883858</v>
       </c>
       <c r="B14" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436146</v>
+        <v>436616</v>
       </c>
       <c r="R14" t="n">
-        <v>7034395</v>
+        <v>7034138</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1960,11 +1965,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1994,7 +1994,7 @@
         <v>133883853</v>
       </c>
       <c r="B15" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 23118-2026 artfynd.xlsx
+++ b/artfynd/A 23118-2026 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133883834</v>
+        <v>133883847</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436935</v>
+        <v>436237</v>
       </c>
       <c r="R3" t="n">
-        <v>7033993</v>
+        <v>7034475</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133883847</v>
+        <v>133883852</v>
       </c>
       <c r="B4" t="n">
         <v>79359</v>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436237</v>
+        <v>436245</v>
       </c>
       <c r="R4" t="n">
-        <v>7034475</v>
+        <v>7034366</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133883833</v>
+        <v>133883855</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436921</v>
+        <v>436337</v>
       </c>
       <c r="R5" t="n">
-        <v>7033984</v>
+        <v>7034305</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133883852</v>
+        <v>133883845</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>91956</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436245</v>
+        <v>436888</v>
       </c>
       <c r="R6" t="n">
-        <v>7034366</v>
+        <v>7034026</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133883832</v>
+        <v>133883856</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436899</v>
+        <v>436376</v>
       </c>
       <c r="R7" t="n">
-        <v>7033975</v>
+        <v>7034270</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,16 +1268,11 @@
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gammalt bohål, ca 2 m upp i tajgagrantickerötad  granhögstubbe. Möjligt tidigare tretå-bohål som sedan använts/utvidgats av andra fåglar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1307,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133883845</v>
+        <v>133883849</v>
       </c>
       <c r="B8" t="n">
-        <v>91956</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436888</v>
+        <v>436262</v>
       </c>
       <c r="R8" t="n">
-        <v>7034026</v>
+        <v>7034464</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,32 +1389,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133883855</v>
+        <v>133883837</v>
       </c>
       <c r="B9" t="n">
-        <v>79359</v>
+        <v>104693</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>222412</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436337</v>
+        <v>436901</v>
       </c>
       <c r="R9" t="n">
-        <v>7034305</v>
+        <v>7034035</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,7 +1486,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133883856</v>
+        <v>133883858</v>
       </c>
       <c r="B10" t="n">
         <v>79359</v>
@@ -1536,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436376</v>
+        <v>436616</v>
       </c>
       <c r="R10" t="n">
-        <v>7034270</v>
+        <v>7034138</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,7 +1583,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133883849</v>
+        <v>133883850</v>
       </c>
       <c r="B11" t="n">
         <v>79359</v>
@@ -1633,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436262</v>
+        <v>436146</v>
       </c>
       <c r="R11" t="n">
-        <v>7034464</v>
+        <v>7034395</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,6 +1654,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133883837</v>
+        <v>133883853</v>
       </c>
       <c r="B12" t="n">
-        <v>104693</v>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436901</v>
+        <v>436328</v>
       </c>
       <c r="R12" t="n">
-        <v>7034035</v>
+        <v>7034303</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,6 +1756,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1792,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133883850</v>
+        <v>133883834</v>
       </c>
       <c r="B13" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1803,21 +1798,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1827,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436146</v>
+        <v>436935</v>
       </c>
       <c r="R13" t="n">
-        <v>7034395</v>
+        <v>7033993</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,7 +1862,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1894,10 +1889,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133883858</v>
+        <v>133883833</v>
       </c>
       <c r="B14" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,21 +1900,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1929,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436616</v>
+        <v>436921</v>
       </c>
       <c r="R14" t="n">
-        <v>7034138</v>
+        <v>7033984</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1965,6 +1960,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1991,10 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133883853</v>
+        <v>133883832</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2002,21 +2002,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436328</v>
+        <v>436899</v>
       </c>
       <c r="R15" t="n">
-        <v>7034303</v>
+        <v>7033975</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,14 +2066,14 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Gammalt bohål, ca 2 m upp i tajgagrantickerötad  granhögstubbe. Möjligt tidigare tretå-bohål som sedan använts/utvidgats av andra fåglar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>

--- a/artfynd/A 23118-2026 artfynd.xlsx
+++ b/artfynd/A 23118-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>133883847</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>133883852</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>133883855</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133883845</v>
+        <v>133883856</v>
       </c>
       <c r="B6" t="n">
-        <v>91956</v>
+        <v>79366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436888</v>
+        <v>436376</v>
       </c>
       <c r="R6" t="n">
-        <v>7034026</v>
+        <v>7034270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133883856</v>
+        <v>133883845</v>
       </c>
       <c r="B7" t="n">
-        <v>79359</v>
+        <v>91963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436376</v>
+        <v>436888</v>
       </c>
       <c r="R7" t="n">
-        <v>7034270</v>
+        <v>7034026</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1295,7 @@
         <v>133883849</v>
       </c>
       <c r="B8" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,32 +1389,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133883837</v>
+        <v>133883850</v>
       </c>
       <c r="B9" t="n">
-        <v>104693</v>
+        <v>79366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436901</v>
+        <v>436146</v>
       </c>
       <c r="R9" t="n">
-        <v>7034035</v>
+        <v>7034395</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,6 +1460,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,7 +1494,7 @@
         <v>133883858</v>
       </c>
       <c r="B10" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,32 +1588,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133883850</v>
+        <v>133883837</v>
       </c>
       <c r="B11" t="n">
-        <v>79359</v>
+        <v>104700</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436146</v>
+        <v>436901</v>
       </c>
       <c r="R11" t="n">
-        <v>7034395</v>
+        <v>7034035</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,11 +1659,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,7 +1688,7 @@
         <v>133883853</v>
       </c>
       <c r="B12" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 23118-2026 artfynd.xlsx
+++ b/artfynd/A 23118-2026 artfynd.xlsx
@@ -675,65 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133883835</v>
+        <v>133883845</v>
       </c>
       <c r="B2" t="n">
-        <v>57162</v>
+        <v>91970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vägbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436192</v>
+        <v>436888</v>
       </c>
       <c r="R2" t="n">
-        <v>7034406</v>
+        <v>7034026</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flertalet tallar i skogen uppvisar tydliga spår efter toppbetning av tjäder.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,11 +775,11 @@
         <v>133883847</v>
       </c>
       <c r="B3" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -899,14 +874,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133883852</v>
+        <v>133883849</v>
       </c>
       <c r="B4" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -934,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436245</v>
+        <v>436262</v>
       </c>
       <c r="R4" t="n">
-        <v>7034366</v>
+        <v>7034464</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,14 +971,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133883855</v>
+        <v>133883850</v>
       </c>
       <c r="B5" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1036,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436337</v>
+        <v>436146</v>
       </c>
       <c r="R5" t="n">
-        <v>7034305</v>
+        <v>7034395</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,14 +1073,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133883856</v>
+        <v>133883852</v>
       </c>
       <c r="B6" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1133,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436376</v>
+        <v>436245</v>
       </c>
       <c r="R6" t="n">
-        <v>7034270</v>
+        <v>7034366</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1144,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133883845</v>
+        <v>133883853</v>
       </c>
       <c r="B7" t="n">
-        <v>91963</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436888</v>
+        <v>436328</v>
       </c>
       <c r="R7" t="n">
-        <v>7034026</v>
+        <v>7034303</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,14 +1277,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133883849</v>
+        <v>133883855</v>
       </c>
       <c r="B8" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1327,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436262</v>
+        <v>436337</v>
       </c>
       <c r="R8" t="n">
-        <v>7034464</v>
+        <v>7034305</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,14 +1374,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133883850</v>
+        <v>133883856</v>
       </c>
       <c r="B9" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1424,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436146</v>
+        <v>436376</v>
       </c>
       <c r="R9" t="n">
-        <v>7034395</v>
+        <v>7034270</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,11 +1445,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,11 +1474,11 @@
         <v>133883858</v>
       </c>
       <c r="B10" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1588,32 +1568,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133883837</v>
+        <v>133883832</v>
       </c>
       <c r="B11" t="n">
-        <v>104700</v>
+        <v>57975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436901</v>
+        <v>436899</v>
       </c>
       <c r="R11" t="n">
-        <v>7034035</v>
+        <v>7033975</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,11 +1641,16 @@
           <t>2026-05-25</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gammalt bohål, ca 2 m upp i tajgagrantickerötad  granhögstubbe. Möjligt tidigare tretå-bohål som sedan använts/utvidgats av andra fåglar.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1685,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133883853</v>
+        <v>133883833</v>
       </c>
       <c r="B12" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436328</v>
+        <v>436921</v>
       </c>
       <c r="R12" t="n">
-        <v>7034303</v>
+        <v>7033984</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,7 +1745,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1889,45 +1874,65 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133883833</v>
+        <v>133883835</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vägbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436921</v>
+        <v>436192</v>
       </c>
       <c r="R14" t="n">
-        <v>7033984</v>
+        <v>7034406</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,7 +1969,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Flertalet tallar i skogen uppvisar tydliga spår efter toppbetning av tjäder.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1991,32 +1996,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133883832</v>
+        <v>133883837</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>104707</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>222412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2026,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436899</v>
+        <v>436901</v>
       </c>
       <c r="R15" t="n">
-        <v>7033975</v>
+        <v>7034035</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2064,16 +2069,11 @@
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Gammalt bohål, ca 2 m upp i tajgagrantickerötad  granhögstubbe. Möjligt tidigare tretå-bohål som sedan använts/utvidgats av andra fåglar.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>

--- a/artfynd/A 23118-2026 artfynd.xlsx
+++ b/artfynd/A 23118-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883847</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883849</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883850</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883852</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883835</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883845</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883853</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883855</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883856</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883858</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883832</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1891,6 +1951,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883833</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1993,6 +2058,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883834</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2090,8 +2160,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883837</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>